--- a/InputData/trans/BNoGP/BAU Number of Gas Pumps.xlsx
+++ b/InputData/trans/BNoGP/BAU Number of Gas Pumps.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10811"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\MN\trans\BNoGP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathaniyer/Library/Containers/com.microsoft.Excel/Data/state-eps-data-repository/MN/trans/BNoGP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95497402-8078-448A-AB10-EF8B0F1F1DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AEAEE6B0-7E09-694B-9147-DBD63B9AEBD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="1110" windowWidth="13035" windowHeight="16890" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="13040" windowHeight="16900" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -831,13 +831,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="2" width="31.85546875" customWidth="1"/>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="2" max="2" width="31.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -845,7 +845,7 @@
         <v>43</v>
       </c>
       <c r="C1" s="8">
-        <v>45258</v>
+        <v>45296</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>81</v>
@@ -854,7 +854,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B2" t="str">
         <f>LOOKUP(B1,E2:F51,F2:F51)</f>
         <v>MN</v>
@@ -866,7 +866,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -880,7 +880,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>3</v>
       </c>
@@ -891,7 +891,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B5" s="3">
         <v>2018</v>
       </c>
@@ -902,7 +902,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -913,7 +913,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -924,7 +924,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E8" s="7" t="s">
         <v>60</v>
       </c>
@@ -932,7 +932,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
@@ -943,7 +943,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -954,7 +954,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E11" s="7" t="s">
         <v>56</v>
       </c>
@@ -962,7 +962,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E12" s="7" t="s">
         <v>55</v>
       </c>
@@ -970,7 +970,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E13" s="7" t="s">
         <v>54</v>
       </c>
@@ -978,7 +978,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E14" s="7" t="s">
         <v>53</v>
       </c>
@@ -986,7 +986,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E15" s="7" t="s">
         <v>52</v>
       </c>
@@ -994,7 +994,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="E16" s="7" t="s">
         <v>51</v>
       </c>
@@ -1002,7 +1002,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E17" s="7" t="s">
         <v>50</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E18" s="7" t="s">
         <v>49</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E19" s="7" t="s">
         <v>48</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E20" s="7" t="s">
         <v>47</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E21" s="7" t="s">
         <v>46</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E22" s="7" t="s">
         <v>45</v>
       </c>
@@ -1050,7 +1050,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E23" s="7" t="s">
         <v>44</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E24" s="7" t="s">
         <v>43</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E25" s="7" t="s">
         <v>42</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E26" s="7" t="s">
         <v>41</v>
       </c>
@@ -1082,7 +1082,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E27" s="7" t="s">
         <v>40</v>
       </c>
@@ -1090,7 +1090,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E28" s="7" t="s">
         <v>38</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E29" s="7" t="s">
         <v>37</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E30" s="7" t="s">
         <v>36</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="31" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E31" s="7" t="s">
         <v>35</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="32" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E32" s="7" t="s">
         <v>34</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E33" s="7" t="s">
         <v>33</v>
       </c>
@@ -1138,7 +1138,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="34" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E34" s="7" t="s">
         <v>32</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="35" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E35" s="7" t="s">
         <v>31</v>
       </c>
@@ -1154,7 +1154,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="36" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E36" s="7" t="s">
         <v>30</v>
       </c>
@@ -1162,7 +1162,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E37" s="7" t="s">
         <v>29</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="38" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E38" s="7" t="s">
         <v>28</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="39" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E39" s="7" t="s">
         <v>27</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="40" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E40" s="7" t="s">
         <v>26</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="41" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E41" s="7" t="s">
         <v>25</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E42" s="7" t="s">
         <v>24</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="43" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E43" s="7" t="s">
         <v>23</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="44" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E44" s="7" t="s">
         <v>22</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="45" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E45" s="7" t="s">
         <v>20</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="46" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E46" s="7" t="s">
         <v>19</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="47" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E47" s="7" t="s">
         <v>18</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="48" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E48" s="7" t="s">
         <v>17</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="49" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E49" s="7" t="s">
         <v>16</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="50" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E50" s="7" t="s">
         <v>14</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="51" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="5:6" x14ac:dyDescent="0.2">
       <c r="E51" s="7" t="s">
         <v>13</v>
       </c>
@@ -1291,13 +1291,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A878A66-DCDA-4DE5-BC74-E1AF8C163921}">
   <dimension ref="A1:P54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" customWidth="1"/>
-    <col min="6" max="6" width="32.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5" customWidth="1"/>
+    <col min="6" max="6" width="32.5" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>79</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -1383,7 +1383,7 @@
         <v>2.7936447399214692E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>1.6208860265755965E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>64</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>1.4423285284608517E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>1.345248723660602E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>6.8701297575605239E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>61</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>1.5229394378039161E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>60</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>9.4999523268815712E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>59</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>2.2189669668628486E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>7.2809853600187228E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>5.9132002531009198E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>56</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>4.4500689093257287E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -1878,7 +1878,7 @@
         <v>2.1582920888626928E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>54</v>
       </c>
@@ -1923,7 +1923,7 @@
         <v>5.9374702043009818E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>3.3813242725515523E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>52</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>2.3472509946346073E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>51</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>1.5229394378039161E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>9.72531615945358E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>1.7275004550615852E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>2.1556917369484004E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -2238,7 +2238,7 @@
         <v>6.9342717714464021E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>46</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>1.4206589291750817E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>1.7838414132045871E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>44</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>3.1464258162938054E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>43</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>1.8731201622619594E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>1.7257668871187234E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>41</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>2.3550520503774843E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>4.4379339337256973E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>8.5984969965935392E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>7.5843597500195028E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>5.07935407258449E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>2.0378091168338115E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>7.3243245585902627E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -2823,7 +2823,7 @@
         <v>4.2879803066681689E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>32</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>3.9854727006388195E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>31</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>4.0478811465818375E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>30</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>3.373523216808675E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>29</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>1.61395175480415E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -3048,7 +3048,7 @@
         <v>8.546489958307691E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>3.3579211053229203E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>26</v>
       </c>
@@ -3138,7 +3138,7 @@
         <v>2.773708708578561E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>25</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>2.2475708379200651E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>24</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>5.4434033405854256E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>23</v>
       </c>
@@ -3273,7 +3273,7 @@
         <v>2.9722022380362142E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>22</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>9.8275966680824139E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>20</v>
       </c>
@@ -3363,7 +3363,7 @@
         <v>7.3503280777331868E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>19</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>3.7271710771524412E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -3453,7 +3453,7 @@
         <v>3.0216089244077697E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>17</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>1.7335679428616007E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>16</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>8.2951226065927589E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>14</v>
       </c>
@@ -3588,7 +3588,7 @@
         <v>2.2692404372058352E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>13</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>2.9123941440074891E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F54" s="10"/>
     </row>
   </sheetData>
@@ -3656,9 +3656,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E66FFDB-7EE3-49F8-8320-71DA73BA9070}">
   <dimension ref="B2:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>80</v>
       </c>
@@ -3678,13 +3678,13 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -3779,7 +3779,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
